--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Qwen2-0.5B-Instruct/Qwen3-4B-Instruct-2507/default/total_votes_file.xlsx
@@ -430,10 +430,10 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>0</v>
